--- a/docs/2/algorithms/Учебный_план_Основы_алгоритмизации_и_программирования.xlsx
+++ b/docs/2/algorithms/Учебный_план_Основы_алгоритмизации_и_программирования.xlsx
@@ -174,7 +174,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -195,12 +195,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Алгоритм и его свойства»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, чем алгоритм отличается от любой последовательности действий, и научитесь проверять запись на дискретность, конечность и результативность.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Алгоритм и его свойства</t>
+          <t xml:space="preserve">исполнитель, дискретность, детерминированность, конечность, массовость</t>
         </is>
       </c>
     </row>
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Блок-схемы и псевдокод»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Научитесь переводить словесное описание в блок-схему по ГОСТ и в псевдокод, чтобы один и тот же алгоритм читался двумя способами.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Блок-схемы и псевдокод</t>
+          <t xml:space="preserve">терминатор, процесс, решение, соединитель, стрелка перехода</t>
         </is>
       </c>
     </row>
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Ввод и вывод: базовые задачи; Арифметические операции: базовые задачи.</t>
+          <t xml:space="preserve">Пишете в VS Code программы, которые читают числа через input и печатают результат арифметики, и сдаёте набор из пяти работающих скриптов с выводом.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ввод и вывод: базовые задачи, Арифметические операции: базовые задачи</t>
+          <t xml:space="preserve">input, int, float, f-строка, деление нацело, остаток</t>
         </is>
       </c>
     </row>
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Переменные, типы и выражения»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, как Python хранит значение в переменной, почему 0.1 + 0.2 даёт хвост и когда неявное приведение типов ломает расчёт.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Переменные, типы и выражения</t>
+          <t xml:space="preserve">переменная, динамическая типизация, приведение типов, приоритет операций, округление</t>
         </is>
       </c>
     </row>
@@ -315,12 +315,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Условия и выбор»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Научитесь строить ветвление на if, elif и else и выбирать между лестницей условий и словарём вариантов, когда ветвей становится много.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Условия и выбор</t>
+          <t xml:space="preserve">if, elif, else, логические операторы, граничный случай</t>
         </is>
       </c>
     </row>
@@ -345,16 +345,16 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Разветвления: базовые задачи; Циклы for: базовые задачи.</t>
+          <t xml:space="preserve">Решаете задачи на выбор варианта и перебор диапазона: программы с if, elif и for, проверенные на наборе входных значений.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разветвления: базовые задачи, Циклы for: базовые задачи</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t xml:space="preserve">range, ветвление, счётчик, накопление суммы, тестовый набор</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
@@ -375,12 +375,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Циклы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сравните for и while, разберёте, откуда берётся бесконечный цикл, и научитесь останавливать перебор через break и continue.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Циклы</t>
+          <t xml:space="preserve">for, while, break, continue, счётчик итераций, условие выхода</t>
         </is>
       </c>
     </row>
@@ -405,12 +405,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Массивы и списки»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, как список хранит элементы по индексам, что делает срез и почему вставка в середину дороже добавления в конец.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Массивы и списки</t>
+          <t xml:space="preserve">индекс, срез, append, вложенный список, длина списка</t>
         </is>
       </c>
     </row>
@@ -435,16 +435,16 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Циклы while: базовые задачи; Вложенные циклы: базовые задачи.</t>
+          <t xml:space="preserve">Пишете программы с while и вложенным перебором: таблицы, суммы рядов и поиск до условия, с проверкой числа итераций.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Циклы while: базовые задачи, Вложенные циклы: базовые задачи</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+          <t xml:space="preserve">while True, вложенный цикл, внешний счётчик, таблица, валидация ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Строки»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Научитесь резать строку по индексам, собирать её из частей и разбирать текст на слова без регулярных выражений.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строки</t>
+          <t xml:space="preserve">неизменяемость, split, join, strip, юникод, форматирование</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Функции и модули»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, зачем выносить код в функцию, как передаются аргументы и как собрать свои функции в модуль, который импортируют другие файлы.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Функции и модули</t>
+          <t xml:space="preserve">def, return, параметр, область видимости, import, докстрока</t>
         </is>
       </c>
     </row>
@@ -525,12 +525,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Строки: базовые задачи; Списки: базовые задачи.</t>
+          <t xml:space="preserve">Обрабатываете текст и наборы данных: подсчёт слов, очистка строк, сортировка списка, и сдаёте скрипты с разбором сложных случаев.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строки: базовые задачи, Списки: базовые задачи</t>
+          <t xml:space="preserve">частота, фильтрация, сортировка, пустой ввод, нормализация</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Словари и множества»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте, как словарь находит значение по ключу за один шаг, чем множество отличается от списка и где теряется порядок элементов.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Словари и множества</t>
+          <t xml:space="preserve">ключ, значение, хеш, set, уникальность, перебор items</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Файлы и обработка данных»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Научитесь читать и записывать текстовые файлы через with, не теряя данные при ошибке, и обрабатывать строки файла построчно.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Файлы и обработка данных</t>
+          <t xml:space="preserve">open, with, режим доступа, кодировка, чтение строк, буфер</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Кортежи: базовые задачи; Словари: базовые задачи.</t>
+          <t xml:space="preserve">Работаете с неизменяемыми наборами и справочниками: кортеж как ключ, словарь как база записей, и сдаёте программу с отчётом по данным.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кортежи: базовые задачи, Словари: базовые задачи</t>
+          <t xml:space="preserve">неизменяемый набор, распаковка, вложенный словарь, get, обновление записи</t>
         </is>
       </c>
     </row>
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Ошибки, исключения и отладка»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разберёте три вида ошибок, научитесь читать трассировку Python и обрабатывать сбой через try, except и finally вместо падения программы.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ошибки, исключения и отладка</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t xml:space="preserve">traceback, исключение, try, except, finally, точка останова</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -675,12 +675,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Базовые алгоритмы сортировки и поиска»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сравните пузырьковую сортировку, сортировку выбором и линейный поиск с бинарным по числу сравнений и условиям применимости.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Базовые алгоритмы сортировки и поиска</t>
+          <t xml:space="preserve">обмен, проход по массиву, бинарный поиск, число сравнений, отсортированный массив, сложность</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Множества: базовые задачи; Функции: базовые задачи.</t>
+          <t xml:space="preserve">Собираете функции для работы с наборами: объединение, пересечение, разность, и оформляете их как модуль с проверочными вызовами.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Множества: базовые задачи, Функции: базовые задачи</t>
+          <t xml:space="preserve">объединение, пересечение, разность, аргумент функции, проверочный вызов</t>
         </is>
       </c>
     </row>
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Рекурсия: базовые задачи; Модули: базовые задачи.</t>
+          <t xml:space="preserve">Пишете рекурсивные функции с базовым случаем и выносите их в отдельный модуль, который импортирует основной скрипт.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рекурсия: базовые задачи, Модули: базовые задачи</t>
+          <t xml:space="preserve">базовый случай, рекурсивный вызов, глубина рекурсии, import, пакет</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Файлы: базовые задачи; Исключения: базовые задачи.</t>
+          <t xml:space="preserve">Строите программу, которая читает файл, перехватывает ошибки формата и записывает журнал обработки, и сдаёте её с набором тестовых файлов.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Файлы: базовые задачи, Исключения: базовые задачи</t>
+          <t xml:space="preserve">FileNotFoundError, ValueError, журнал, разбор строки, кодировка</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Сортировка: базовые задачи; Поиск: базовые задачи.</t>
+          <t xml:space="preserve">Реализуете сортировку и поиск на реальных наборах, замеряете число сравнений и сравниваете результат со встроенной функцией sorted.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сортировка: базовые задачи, Поиск: базовые задачи</t>
+          <t xml:space="preserve">устойчивость, sorted, ключ сортировки, линейный поиск, счётчик сравнений</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Двумерные массивы: базовые задачи; Алгоритмы на графах: базовые задачи.</t>
+          <t xml:space="preserve">Обрабатываете таблицу как вложенный список и обходите граф в ширину, сдавая программу с выводом пути и матрицы смежности.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Двумерные массивы: базовые задачи, Алгоритмы на графах: базовые задачи</t>
+          <t xml:space="preserve">вложенный список, матрица смежности, обход в ширину, очередь, путь</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Динамическое программирование: базовые задачи; Жадные алгоритмы: базовые задачи.</t>
+          <t xml:space="preserve">Решаете задачи, где жадный выбор не всегда верен, и сравниваете его с таблицей динамического программирования на одних данных.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамическое программирование: базовые задачи, Жадные алгоритмы: базовые задачи</t>
+          <t xml:space="preserve">подзадача, таблица значений, жадный выбор, контрпример, оптимальность</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Битовые операции: базовые задачи; Регулярные выражения: базовые задачи.</t>
+          <t xml:space="preserve">Работаете с двоичным представлением числа и разбираете строки шаблоном: маски, сдвиги и поиск по регулярному выражению.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Битовые операции: базовые задачи, Регулярные выражения: базовые задачи</t>
+          <t xml:space="preserve">битовая маска, сдвиг, xor, шаблон, группа, re</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Генераторы: базовые задачи; Декораторы: базовые задачи.</t>
+          <t xml:space="preserve">Пишете генератор, который отдаёт значения по одному, и оборачиваете функцию декоратором для замера времени и логирования.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Генераторы: базовые задачи, Декораторы: базовые задачи</t>
+          <t xml:space="preserve">yield, итератор, ленивое вычисление, замыкание, обёртка, functools</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: ООП: базовые задачи; Наследование: базовые задачи.</t>
+          <t xml:space="preserve">Описываете предметную область классами с полями и методами и выносите общее поведение в базовый класс, сдавая модель из трёх классов.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООП: базовые задачи, Наследование: базовые задачи</t>
+          <t xml:space="preserve">класс, экземпляр, метод, иерархия классов, переопределение, super</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Тестирование: базовые задачи; Отладка: базовые задачи.</t>
+          <t xml:space="preserve">Пишете проверки для своих функций и находите ошибку в чужом коде по трассировке, сдавая набор тестов и отчёт о найденном дефекте.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование: базовые задачи, Отладка: базовые задачи</t>
+          <t xml:space="preserve">assert, тестовый набор, граничное значение, точка останова, дефект</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Работа с JSON: базовые задачи; Работа с CSV: базовые задачи.</t>
+          <t xml:space="preserve">Читаете и записываете обменные форматы: разбираете JSON в словарь и таблицу CSV в список строк, сдавая конвертер между форматами.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Работа с JSON: базовые задачи, Работа с CSV: базовые задачи</t>
+          <t xml:space="preserve">json.load, сериализация, разделитель, заголовок, DictReader</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Мини-проект: базовые задачи; Итоговая работа: базовые задачи.</t>
+          <t xml:space="preserve">Собираете небольшую программу из готовых функций: ввод, обработка, сохранение отчёта, и защищаете её по чек-листу требований.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мини-проект: базовые задачи, Итоговая работа: базовые задачи</t>
+          <t xml:space="preserve">структура проекта, главная функция, обработка ввода, отчёт, защита работы</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Ввод и вывод: прикладные задачи; Арифметические операции: прикладные задачи.</t>
+          <t xml:space="preserve">Решаете расчётные задачи с реальными данными: стоимость, скидка, перевод единиц, и сдаёте скрипт с проверкой на крайних значениях.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ввод и вывод: прикладные задачи, Арифметические операции: прикладные задачи</t>
+          <t xml:space="preserve">формула, округление, единицы измерения, наценка, проверка расчёта</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Разветвления: прикладные задачи; Циклы for: прикладные задачи.</t>
+          <t xml:space="preserve">Строите программу с выбором тарифа и накоплением итога по диапазону, сдавая её с таблицей результатов по нескольким входам.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разветвления: прикладные задачи, Циклы for: прикладные задачи</t>
+          <t xml:space="preserve">тариф, диапазон, накопитель, шаг цикла, таблица результатов</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Циклы while: прикладные задачи; Вложенные циклы: прикладные задачи.</t>
+          <t xml:space="preserve">Моделируете процесс с условием остановки и строите сетку значений вложенным циклом, сдавая программу с журналом шагов.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Циклы while: прикладные задачи, Вложенные циклы: прикладные задачи</t>
+          <t xml:space="preserve">условие остановки, моделирование, сетка значений, журнал шагов, итерация</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Строки: прикладные задачи; Списки: прикладные задачи.</t>
+          <t xml:space="preserve">Разбираете текстовый отчёт: выделяете поля, считаете показатели по строкам и собираете сводку в список, готовый к выводу.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строки: прикладные задачи, Списки: прикладные задачи</t>
+          <t xml:space="preserve">разделитель, поле отчёта, сводка, среднее, форматирование вывода</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Кортежи: прикладные задачи; Словари: прикладные задачи.</t>
+          <t xml:space="preserve">Храните справочник записей в словаре и используете кортеж как составной ключ, сдавая программу поиска и обновления записей.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кортежи: прикладные задачи, Словари: прикладные задачи</t>
+          <t xml:space="preserve">составной ключ, справочник, поиск записи, сортировка ключей, обновление</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Множества: прикладные задачи; Функции: прикладные задачи.</t>
+          <t xml:space="preserve">Сравниваете два набора данных через множества и оформляете проверку как функцию, которую вызывают из основного сценария.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Множества: прикладные задачи, Функции: прикладные задачи</t>
+          <t xml:space="preserve">разность множеств, пересечение, симметричная разность, возврат значения, повторный вызов</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Рекурсия: прикладные задачи; Модули: прикладные задачи.</t>
+          <t xml:space="preserve">Реализуете обход вложенной структуры рекурсией и разносите код по двум модулям с общим пакетом, сдавая рабочую сборку.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рекурсия: прикладные задачи, Модули: прикладные задачи</t>
+          <t xml:space="preserve">вложенная структура, рекурсивный обход, пакет, относительный импорт, точка входа</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Файлы: прикладные задачи; Исключения: прикладные задачи.</t>
+          <t xml:space="preserve">Строите обработчик журнала: читает файл построчно, пропускает битые строки с записью в отчёт и сохраняет очищенные данные.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Файлы: прикладные задачи, Исключения: прикладные задачи</t>
+          <t xml:space="preserve">построчное чтение, битая строка, отчёт об ошибках, очистка данных, дозапись</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Сортировка: прикладные задачи; Поиск: прикладные задачи.</t>
+          <t xml:space="preserve">Сортируете каталог по нескольким ключам и ищете записи по частичному совпадению, сдавая программу с замерами времени.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сортировка: прикладные задачи, Поиск: прикладные задачи</t>
+          <t xml:space="preserve">составной ключ, частичное совпадение, time, индекс, бинарный поиск</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Двумерные массивы: прикладные задачи; Алгоритмы на графах: прикладные задачи.</t>
+          <t xml:space="preserve">Строите матрицу расстояний по карте дорог и находите кратчайший путь обходом графа, сдавая программу с картой и маршрутом.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Двумерные массивы: прикладные задачи, Алгоритмы на графах: прикладные задачи</t>
+          <t xml:space="preserve">матрица смежности, кратчайший путь, обход в ширину, маршрут, вес ребра</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Динамическое программирование: прикладные задачи; Жадные алгоритмы: прикладные задачи.</t>
+          <t xml:space="preserve">Решаете задачу о размене и задачу о расписании двумя подходами, сравниваете ответы и объясняете расхождение в отчёте.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Динамическое программирование: прикладные задачи, Жадные алгоритмы: прикладные задачи</t>
+          <t xml:space="preserve">размен, расписание, таблица решений, жадное правило, контрпример</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Битовые операции: прикладные задачи; Регулярные выражения: прикладные задачи.</t>
+          <t xml:space="preserve">Кодируете набор флагов в одном числе и проверяете формат данных шаблоном, сдавая программу разбора и валидации строк.</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Битовые операции: прикладные задачи, Регулярные выражения: прикладные задачи</t>
+          <t xml:space="preserve">флаг, маска, сдвиг влево, валидация, именованная группа, re.fullmatch</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Генераторы: прикладные задачи; Декораторы: прикладные задачи.</t>
+          <t xml:space="preserve">Обрабатываете поток записей генератором и добавляете к функциям замер времени, не меняя их код, сдавая программу с отчётом.</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Генераторы: прикладные задачи, Декораторы: прикладные задачи</t>
+          <t xml:space="preserve">поток данных, yield, замыкание, обёртка, время вызова, лог</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: ООП: прикладные задачи; Наследование: прикладные задачи.</t>
+          <t xml:space="preserve">Проектируете иерархию классов для учёта техники и проверяете её на наборе объектов, сдавая диаграмму и работающий код.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ООП: прикладные задачи, Наследование: прикладные задачи</t>
+          <t xml:space="preserve">базовый класс, наследник, полиморфизм, переопределение, иерархия</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Тестирование: прикладные задачи; Отладка: прикладные задачи.</t>
+          <t xml:space="preserve">Покрываете готовый модуль проверками и устраняете найденный дефект, сдавая набор тестов и описание исправления.</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование: прикладные задачи, Отладка: прикладные задачи</t>
+          <t xml:space="preserve">покрытие ветвей, падающий тест, регрессия, assert, исправление</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Работа с JSON: прикладные задачи; Работа с CSV: прикладные задачи.</t>
+          <t xml:space="preserve">Переносите данные между JSON и CSV без потери полей, сдавая конвертер, который проверен на файле с вложенными записями.</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Работа с JSON: прикладные задачи, Работа с CSV: прикладные задачи</t>
+          <t xml:space="preserve">вложенный объект, плоская таблица, экранирование, обратное преобразование, кодировка</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Мини-проект: прикладные задачи; Итоговая работа: прикладные задачи.</t>
+          <t xml:space="preserve">Собираете приложение для учёта заявок с хранением в файле и защищаете его по требованиям к интерфейсу и обработке ошибок.</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мини-проект: прикладные задачи, Итоговая работа: прикладные задачи</t>
+          <t xml:space="preserve">заявка, хранение, структура модулей, сценарий пользователя, защита</t>
         </is>
       </c>
     </row>

--- a/docs/2/algorithms/Учебный_план_Основы_алгоритмизации_и_программирования.xlsx
+++ b/docs/2/algorithms/Учебный_план_Основы_алгоритмизации_и_программирования.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D39" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D40" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D41" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="D42" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="D43" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D44" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="D45" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D46" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="D47" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="D48" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="D49" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="D50" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="D51" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D52" s="6">
-        <v>7200</v>
+        <v>160</v>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>

--- a/docs/2/algorithms/Учебный_план_Основы_алгоритмизации_и_программирования.xlsx
+++ b/docs/2/algorithms/Учебный_план_Основы_алгоритмизации_и_программирования.xlsx
@@ -237,60 +237,60 @@
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Ввод и вывод: базовые задачи; Арифметические операции: базовые задачи</t>
+          <t xml:space="preserve">Лекция 3. Переменные, типы и выражения</t>
         </is>
       </c>
       <c r="D8" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пишете в VS Code программы, которые читают числа через input и печатают результат арифметики, и сдаёте набор из пяти работающих скриптов с выводом.</t>
+          <t xml:space="preserve">Разберёте, как Python хранит значение в переменной, почему 0.1 + 0.2 даёт хвост и когда неявное приведение типов ломает расчёт.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">input, int, float, f-строка, деление нацело, остаток</t>
+          <t xml:space="preserve">переменная, динамическая типизация, приведение типов, приоритет операций, округление</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4-5</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. Переменные, типы и выражения</t>
+          <t xml:space="preserve">Практика 1. Ввод и вывод: базовые задачи; Арифметические операции: базовые задачи</t>
         </is>
       </c>
       <c r="D9" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте, как Python хранит значение в переменной, почему 0.1 + 0.2 даёт хвост и когда неявное приведение типов ломает расчёт.</t>
+          <t xml:space="preserve">Пишете в VS Code программы, которые читают числа через input и печатают результат арифметики, и сдаёте набор из пяти работающих скриптов с выводом.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">переменная, динамическая типизация, приведение типов, приоритет операций, округление</t>
+          <t xml:space="preserve">input, int, float, f-строка, деление нацело, остаток</t>
         </is>
       </c>
     </row>
@@ -327,120 +327,120 @@
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Разветвления: базовые задачи; Циклы for: базовые задачи</t>
+          <t xml:space="preserve">Лекция 5. Циклы</t>
         </is>
       </c>
       <c r="D11" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Решаете задачи на выбор варианта и перебор диапазона: программы с if, elif и for, проверенные на наборе входных значений.</t>
+          <t xml:space="preserve">Сравните for и while, разберёте, откуда берётся бесконечный цикл, и научитесь останавливать перебор через break и continue.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">range, ветвление, счётчик, накопление суммы, тестовый набор</t>
+          <t xml:space="preserve">for, while, break, continue, счётчик итераций, условие выхода</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8-9</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. Циклы</t>
+          <t xml:space="preserve">Практика 2. Разветвления: базовые задачи; Циклы for: базовые задачи</t>
         </is>
       </c>
       <c r="D12" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравните for и while, разберёте, откуда берётся бесконечный цикл, и научитесь останавливать перебор через break и continue.</t>
+          <t xml:space="preserve">Решаете задачи на выбор варианта и перебор диапазона: программы с if, elif и for, проверенные на наборе входных значений.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">for, while, break, continue, счётчик итераций, условие выхода</t>
+          <t xml:space="preserve">range, ветвление, счётчик, накопление суммы, тестовый набор</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">10-11</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. Массивы и списки</t>
+          <t xml:space="preserve">Практика 3. Циклы while: базовые задачи; Вложенные циклы: базовые задачи</t>
         </is>
       </c>
       <c r="D13" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте, как список хранит элементы по индексам, что делает срез и почему вставка в середину дороже добавления в конец.</t>
+          <t xml:space="preserve">Пишете программы с while и вложенным перебором: таблицы, суммы рядов и поиск до условия, с проверкой числа итераций.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">индекс, срез, append, вложенный список, длина списка</t>
+          <t xml:space="preserve">while True, вложенный цикл, внешний счётчик, таблица, валидация ввода</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11-12</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Циклы while: базовые задачи; Вложенные циклы: базовые задачи</t>
+          <t xml:space="preserve">Лекция 6. Массивы и списки</t>
         </is>
       </c>
       <c r="D14" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пишете программы с while и вложенным перебором: таблицы, суммы рядов и поиск до условия, с проверкой числа итераций.</t>
+          <t xml:space="preserve">Разберёте, как список хранит элементы по индексам, что делает срез и почему вставка в середину дороже добавления в конец.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">while True, вложенный цикл, внешний счётчик, таблица, валидация ввода</t>
+          <t xml:space="preserve">индекс, срез, append, вложенный список, длина списка</t>
         </is>
       </c>
     </row>
@@ -477,60 +477,60 @@
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">14-15</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Функции и модули</t>
+          <t xml:space="preserve">Практика 4. Строки: базовые задачи; Списки: базовые задачи</t>
         </is>
       </c>
       <c r="D16" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте, зачем выносить код в функцию, как передаются аргументы и как собрать свои функции в модуль, который импортируют другие файлы.</t>
+          <t xml:space="preserve">Обрабатываете текст и наборы данных: подсчёт слов, очистка строк, сортировка списка, и сдаёте скрипты с разбором сложных случаев.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">def, return, параметр, область видимости, import, докстрока</t>
+          <t xml:space="preserve">частота, фильтрация, сортировка, пустой ввод, нормализация</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15-16</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Строки: базовые задачи; Списки: базовые задачи</t>
+          <t xml:space="preserve">Лекция 8. Функции и модули</t>
         </is>
       </c>
       <c r="D17" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обрабатываете текст и наборы данных: подсчёт слов, очистка строк, сортировка списка, и сдаёте скрипты с разбором сложных случаев.</t>
+          <t xml:space="preserve">Разберёте, зачем выносить код в функцию, как передаются аргументы и как собрать свои функции в модуль, который импортируют другие файлы.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">частота, фильтрация, сортировка, пустой ввод, нормализация</t>
+          <t xml:space="preserve">def, return, параметр, область видимости, import, докстрока</t>
         </is>
       </c>
     </row>
@@ -567,37 +567,37 @@
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">18-19</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Файлы и обработка данных</t>
+          <t xml:space="preserve">Практика 5. Кортежи: базовые задачи; Словари: базовые задачи</t>
         </is>
       </c>
       <c r="D19" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Научитесь читать и записывать текстовые файлы через with, не теряя данные при ошибке, и обрабатывать строки файла построчно.</t>
+          <t xml:space="preserve">Работаете с неизменяемыми наборами и справочниками: кортеж как ключ, словарь как база записей, и сдаёте программу с отчётом по данным.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">open, with, режим доступа, кодировка, чтение строк, буфер</t>
+          <t xml:space="preserve">неизменяемый набор, распаковка, вложенный словарь, get, обновление записи</t>
         </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-20</t>
+          <t xml:space="preserve">20-21</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Кортежи: базовые задачи; Словари: базовые задачи</t>
+          <t xml:space="preserve">Практика 6. Множества: базовые задачи; Функции: базовые задачи</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,19 +615,19 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Работаете с неизменяемыми наборами и справочниками: кортеж как ключ, словарь как база записей, и сдаёте программу с отчётом по данным.</t>
+          <t xml:space="preserve">Собираете функции для работы с наборами: объединение, пересечение, разность, и оформляете их как модуль с проверочными вызовами.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">неизменяемый набор, распаковка, вложенный словарь, get, обновление записи</t>
+          <t xml:space="preserve">объединение, пересечение, разность, аргумент функции, проверочный вызов</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Ошибки, исключения и отладка</t>
+          <t xml:space="preserve">Лекция 10. Файлы и обработка данных</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -645,19 +645,19 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разберёте три вида ошибок, научитесь читать трассировку Python и обрабатывать сбой через try, except и finally вместо падения программы.</t>
+          <t xml:space="preserve">Научитесь читать и записывать текстовые файлы через with, не теряя данные при ошибке, и обрабатывать строки файла построчно.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">traceback, исключение, try, except, finally, точка останова</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+          <t xml:space="preserve">open, with, режим доступа, кодировка, чтение строк, буфер</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Базовые алгоритмы сортировки и поиска</t>
+          <t xml:space="preserve">Лекция 11. Ошибки, исключения и отладка</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,42 +675,42 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Разберёте три вида ошибок, научитесь читать трассировку Python и обрабатывать сбой через try, except и finally вместо падения программы.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">traceback, исключение, try, except, finally, точка останова</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 12. Базовые алгоритмы сортировки и поиска</t>
+        </is>
+      </c>
+      <c r="D23" s="6">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Сравните пузырьковую сортировку, сортировку выбором и линейный поиск с бинарным по числу сравнений и условиям применимости.</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">обмен, проход по массиву, бинарный поиск, число сравнений, отсортированный массив, сложность</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23-24</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 6. Множества: базовые задачи; Функции: базовые задачи</t>
-        </is>
-      </c>
-      <c r="D23" s="6">
-        <v>4</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Собираете функции для работы с наборами: объединение, пересечение, разность, и оформляете их как модуль с проверочными вызовами.</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">объединение, пересечение, разность, аргумент функции, проверочный вызов</t>
         </is>
       </c>
     </row>
